--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2020_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2020_T3_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="51">
   <si>
     <t/>
   </si>
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,51 +57,54 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.316</t>
-  </si>
-  <si>
-    <t>(0.054)</t>
+    <t>0.343</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>0.543</t>
+  </si>
+  <si>
+    <t>(0.060)</t>
+  </si>
+  <si>
+    <t>0.300</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>1.371</t>
+  </si>
+  <si>
+    <t>(0.456)</t>
+  </si>
+  <si>
+    <t>1.314</t>
+  </si>
+  <si>
+    <t>(0.204)</t>
+  </si>
+  <si>
+    <t>0.486</t>
+  </si>
+  <si>
+    <t>(0.111)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>0.500</t>
   </si>
   <si>
-    <t>(0.058)</t>
-  </si>
-  <si>
-    <t>0.276</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>1.263</t>
-  </si>
-  <si>
-    <t>(0.422)</t>
-  </si>
-  <si>
-    <t>1.211</t>
-  </si>
-  <si>
-    <t>(0.192)</t>
-  </si>
-  <si>
-    <t>0.447</t>
-  </si>
-  <si>
-    <t>(0.103)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>(0.080)</t>
   </si>
   <si>
@@ -135,7 +138,7 @@
     <t>(0.290)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -147,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.184*</t>
-  </si>
-  <si>
-    <t>0.325***</t>
-  </si>
-  <si>
-    <t>0.399***</t>
-  </si>
-  <si>
-    <t>0.987</t>
-  </si>
-  <si>
-    <t>2.514***</t>
-  </si>
-  <si>
-    <t>1.153***</t>
+    <t>0.157</t>
+  </si>
+  <si>
+    <t>0.282***</t>
+  </si>
+  <si>
+    <t>0.375***</t>
+  </si>
+  <si>
+    <t>0.879</t>
+  </si>
+  <si>
+    <t>2.411***</t>
+  </si>
+  <si>
+    <t>1.114***</t>
   </si>
 </sst>
 </file>
@@ -229,7 +232,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -252,7 +255,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -275,7 +278,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -292,13 +295,13 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -315,7 +318,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -338,13 +341,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -361,7 +364,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -384,13 +387,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -407,7 +410,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -430,13 +433,13 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -453,7 +456,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -476,13 +479,13 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -499,7 +502,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -522,13 +525,13 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -545,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
